--- a/Docs/Lab03/Lab03_WBT_TCs_Form.xlsx
+++ b/Docs/Lab03/Lab03_WBT_TCs_Form.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64CC18EF-80B7-4743-90B2-D73F9666F79F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F612B6DA-1AE8-403D-B809-5218114D6DBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -1345,7 +1345,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1392,6 +1392,60 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1404,6 +1458,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1413,9 +1473,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1443,12 +1500,24 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1461,220 +1530,145 @@
     <xf numFmtId="0" fontId="13" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2105,12 +2099,12 @@
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B1" s="8"/>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="28"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="46"/>
     </row>
     <row r="2" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B2" s="25" t="s">
@@ -2247,73 +2241,73 @@
   <sheetData>
     <row r="1" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B1" s="8"/>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="28"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="46"/>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="32"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="6" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="28"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="46"/>
       <c r="F6" s="18"/>
       <c r="G6" s="18"/>
-      <c r="I6" s="26" t="s">
+      <c r="I6" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="27"/>
-      <c r="K6" s="27"/>
-      <c r="L6" s="27"/>
-      <c r="M6" s="27"/>
-      <c r="N6" s="27"/>
-      <c r="O6" s="27"/>
-      <c r="Q6" s="26" t="s">
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="45"/>
+      <c r="M6" s="45"/>
+      <c r="N6" s="45"/>
+      <c r="O6" s="45"/>
+      <c r="Q6" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="R6" s="27"/>
-      <c r="S6" s="27"/>
-      <c r="T6" s="27"/>
+      <c r="R6" s="45"/>
+      <c r="S6" s="45"/>
+      <c r="T6" s="45"/>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B8" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="44" t="s">
+      <c r="C8" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="62"/>
       <c r="F8" s="20"/>
       <c r="G8" s="20"/>
       <c r="I8" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="Q8" s="43" t="s">
+      <c r="Q8" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="R8" s="43"/>
-      <c r="S8" s="43"/>
+      <c r="R8" s="49"/>
+      <c r="S8" s="49"/>
       <c r="T8" s="21">
         <v>5</v>
       </c>
@@ -2322,19 +2316,19 @@
       <c r="B9" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
       <c r="F9" s="23"/>
       <c r="G9" s="23"/>
       <c r="I9" s="24"/>
-      <c r="Q9" s="43" t="s">
+      <c r="Q9" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="R9" s="43"/>
-      <c r="S9" s="43"/>
+      <c r="R9" s="49"/>
+      <c r="S9" s="49"/>
       <c r="T9" s="21" t="s">
         <v>84</v>
       </c>
@@ -2343,29 +2337,29 @@
       <c r="B10" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
       <c r="F10" s="23"/>
       <c r="G10" s="23"/>
-      <c r="I10" s="34" t="e" vm="1">
+      <c r="I10" s="53" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="J10" s="35"/>
-      <c r="K10" s="35"/>
-      <c r="L10" s="35"/>
-      <c r="M10" s="35"/>
-      <c r="N10" s="35"/>
-      <c r="O10" s="36"/>
-      <c r="Q10" s="43" t="s">
+      <c r="J10" s="54"/>
+      <c r="K10" s="54"/>
+      <c r="L10" s="54"/>
+      <c r="M10" s="54"/>
+      <c r="N10" s="54"/>
+      <c r="O10" s="55"/>
+      <c r="Q10" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="R10" s="43" t="s">
+      <c r="R10" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="S10" s="43"/>
+      <c r="S10" s="49"/>
       <c r="T10" s="21" t="s">
         <v>85</v>
       </c>
@@ -2374,239 +2368,228 @@
       <c r="B11" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="33" t="s">
+      <c r="C11" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
       <c r="F11" s="23"/>
       <c r="G11" s="23"/>
-      <c r="I11" s="37"/>
-      <c r="J11" s="38"/>
-      <c r="K11" s="38"/>
-      <c r="L11" s="38"/>
-      <c r="M11" s="38"/>
-      <c r="N11" s="38"/>
-      <c r="O11" s="39"/>
+      <c r="I11" s="56"/>
+      <c r="J11" s="57"/>
+      <c r="K11" s="57"/>
+      <c r="L11" s="57"/>
+      <c r="M11" s="57"/>
+      <c r="N11" s="57"/>
+      <c r="O11" s="58"/>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B12" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48"/>
       <c r="F12" s="23"/>
       <c r="G12" s="23"/>
-      <c r="I12" s="37"/>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="38"/>
-      <c r="O12" s="39"/>
+      <c r="I12" s="56"/>
+      <c r="J12" s="57"/>
+      <c r="K12" s="57"/>
+      <c r="L12" s="57"/>
+      <c r="M12" s="57"/>
+      <c r="N12" s="57"/>
+      <c r="O12" s="58"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B13" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="33" t="s">
+      <c r="C13" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="48"/>
       <c r="F13" s="23"/>
       <c r="G13" s="23"/>
-      <c r="I13" s="37"/>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-      <c r="L13" s="38"/>
-      <c r="M13" s="38"/>
-      <c r="N13" s="38"/>
-      <c r="O13" s="39"/>
-      <c r="Q13" s="26" t="s">
+      <c r="I13" s="56"/>
+      <c r="J13" s="57"/>
+      <c r="K13" s="57"/>
+      <c r="L13" s="57"/>
+      <c r="M13" s="57"/>
+      <c r="N13" s="57"/>
+      <c r="O13" s="58"/>
+      <c r="Q13" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="R13" s="27"/>
-      <c r="S13" s="27"/>
-      <c r="T13" s="27"/>
+      <c r="R13" s="45"/>
+      <c r="S13" s="45"/>
+      <c r="T13" s="45"/>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B14" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
       <c r="F14" s="23"/>
       <c r="G14" s="23"/>
-      <c r="I14" s="37"/>
-      <c r="J14" s="38"/>
-      <c r="K14" s="38"/>
-      <c r="L14" s="38"/>
-      <c r="M14" s="38"/>
-      <c r="N14" s="38"/>
-      <c r="O14" s="39"/>
+      <c r="I14" s="56"/>
+      <c r="J14" s="57"/>
+      <c r="K14" s="57"/>
+      <c r="L14" s="57"/>
+      <c r="M14" s="57"/>
+      <c r="N14" s="57"/>
+      <c r="O14" s="58"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I15" s="37"/>
-      <c r="J15" s="38"/>
-      <c r="K15" s="38"/>
-      <c r="L15" s="38"/>
-      <c r="M15" s="38"/>
-      <c r="N15" s="38"/>
-      <c r="O15" s="39"/>
+      <c r="I15" s="56"/>
+      <c r="J15" s="57"/>
+      <c r="K15" s="57"/>
+      <c r="L15" s="57"/>
+      <c r="M15" s="57"/>
+      <c r="N15" s="57"/>
+      <c r="O15" s="58"/>
       <c r="Q15" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="R15" s="44" t="s">
+      <c r="R15" s="62" t="s">
         <v>33</v>
       </c>
-      <c r="S15" s="44"/>
-      <c r="T15" s="44"/>
+      <c r="S15" s="62"/>
+      <c r="T15" s="62"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I16" s="37"/>
-      <c r="J16" s="38"/>
-      <c r="K16" s="38"/>
-      <c r="L16" s="38"/>
-      <c r="M16" s="38"/>
-      <c r="N16" s="38"/>
-      <c r="O16" s="39"/>
-      <c r="Q16" s="92" t="s">
+      <c r="I16" s="56"/>
+      <c r="J16" s="57"/>
+      <c r="K16" s="57"/>
+      <c r="L16" s="57"/>
+      <c r="M16" s="57"/>
+      <c r="N16" s="57"/>
+      <c r="O16" s="58"/>
+      <c r="Q16" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="R16" s="29" t="s">
+      <c r="R16" s="47" t="s">
         <v>86</v>
       </c>
-      <c r="S16" s="29"/>
-      <c r="T16" s="29"/>
+      <c r="S16" s="47"/>
+      <c r="T16" s="47"/>
     </row>
     <row r="17" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I17" s="37"/>
-      <c r="J17" s="38"/>
-      <c r="K17" s="38"/>
-      <c r="L17" s="38"/>
-      <c r="M17" s="38"/>
-      <c r="N17" s="38"/>
-      <c r="O17" s="39"/>
-      <c r="Q17" s="92" t="s">
+      <c r="I17" s="56"/>
+      <c r="J17" s="57"/>
+      <c r="K17" s="57"/>
+      <c r="L17" s="57"/>
+      <c r="M17" s="57"/>
+      <c r="N17" s="57"/>
+      <c r="O17" s="58"/>
+      <c r="Q17" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="R17" s="29" t="s">
+      <c r="R17" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="S17" s="29"/>
-      <c r="T17" s="29"/>
+      <c r="S17" s="47"/>
+      <c r="T17" s="47"/>
     </row>
     <row r="18" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I18" s="37"/>
-      <c r="J18" s="38"/>
-      <c r="K18" s="38"/>
-      <c r="L18" s="38"/>
-      <c r="M18" s="38"/>
-      <c r="N18" s="38"/>
-      <c r="O18" s="39"/>
-      <c r="Q18" s="92" t="s">
+      <c r="I18" s="56"/>
+      <c r="J18" s="57"/>
+      <c r="K18" s="57"/>
+      <c r="L18" s="57"/>
+      <c r="M18" s="57"/>
+      <c r="N18" s="57"/>
+      <c r="O18" s="58"/>
+      <c r="Q18" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="R18" s="29" t="s">
+      <c r="R18" s="47" t="s">
         <v>88</v>
       </c>
-      <c r="S18" s="29"/>
-      <c r="T18" s="29"/>
+      <c r="S18" s="47"/>
+      <c r="T18" s="47"/>
     </row>
     <row r="19" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I19" s="37"/>
-      <c r="J19" s="38"/>
-      <c r="K19" s="38"/>
-      <c r="L19" s="38"/>
-      <c r="M19" s="38"/>
-      <c r="N19" s="38"/>
-      <c r="O19" s="39"/>
-      <c r="Q19" s="92" t="s">
+      <c r="I19" s="56"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="57"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="58"/>
+      <c r="Q19" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="R19" s="29" t="s">
+      <c r="R19" s="47" t="s">
         <v>90</v>
       </c>
-      <c r="S19" s="29"/>
-      <c r="T19" s="29"/>
+      <c r="S19" s="47"/>
+      <c r="T19" s="47"/>
     </row>
     <row r="20" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I20" s="37"/>
-      <c r="J20" s="38"/>
-      <c r="K20" s="38"/>
-      <c r="L20" s="38"/>
-      <c r="M20" s="38"/>
-      <c r="N20" s="38"/>
-      <c r="O20" s="39"/>
-      <c r="Q20" s="92" t="s">
+      <c r="I20" s="56"/>
+      <c r="J20" s="57"/>
+      <c r="K20" s="57"/>
+      <c r="L20" s="57"/>
+      <c r="M20" s="57"/>
+      <c r="N20" s="57"/>
+      <c r="O20" s="58"/>
+      <c r="Q20" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="R20" s="29" t="s">
+      <c r="R20" s="47" t="s">
         <v>92</v>
       </c>
-      <c r="S20" s="29"/>
-      <c r="T20" s="29"/>
+      <c r="S20" s="47"/>
+      <c r="T20" s="47"/>
     </row>
     <row r="21" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I21" s="37"/>
-      <c r="J21" s="38"/>
-      <c r="K21" s="38"/>
-      <c r="L21" s="38"/>
-      <c r="M21" s="38"/>
-      <c r="N21" s="38"/>
-      <c r="O21" s="39"/>
+      <c r="I21" s="56"/>
+      <c r="J21" s="57"/>
+      <c r="K21" s="57"/>
+      <c r="L21" s="57"/>
+      <c r="M21" s="57"/>
+      <c r="N21" s="57"/>
+      <c r="O21" s="58"/>
       <c r="Q21" s="22"/>
-      <c r="R21" s="29"/>
-      <c r="S21" s="29"/>
-      <c r="T21" s="29"/>
+      <c r="R21" s="47"/>
+      <c r="S21" s="47"/>
+      <c r="T21" s="47"/>
     </row>
     <row r="22" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I22" s="37"/>
-      <c r="J22" s="38"/>
-      <c r="K22" s="38"/>
-      <c r="L22" s="38"/>
-      <c r="M22" s="38"/>
-      <c r="N22" s="38"/>
-      <c r="O22" s="39"/>
+      <c r="I22" s="56"/>
+      <c r="J22" s="57"/>
+      <c r="K22" s="57"/>
+      <c r="L22" s="57"/>
+      <c r="M22" s="57"/>
+      <c r="N22" s="57"/>
+      <c r="O22" s="58"/>
     </row>
     <row r="23" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I23" s="37"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
-      <c r="L23" s="38"/>
-      <c r="M23" s="38"/>
-      <c r="N23" s="38"/>
-      <c r="O23" s="39"/>
+      <c r="I23" s="56"/>
+      <c r="J23" s="57"/>
+      <c r="K23" s="57"/>
+      <c r="L23" s="57"/>
+      <c r="M23" s="57"/>
+      <c r="N23" s="57"/>
+      <c r="O23" s="58"/>
     </row>
     <row r="24" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I24" s="40"/>
-      <c r="J24" s="41"/>
-      <c r="K24" s="41"/>
-      <c r="L24" s="41"/>
-      <c r="M24" s="41"/>
-      <c r="N24" s="41"/>
-      <c r="O24" s="42"/>
+      <c r="I24" s="59"/>
+      <c r="J24" s="60"/>
+      <c r="K24" s="60"/>
+      <c r="L24" s="60"/>
+      <c r="M24" s="60"/>
+      <c r="N24" s="60"/>
+      <c r="O24" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="R20:T20"/>
-    <mergeCell ref="R17:T17"/>
-    <mergeCell ref="R19:T19"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="Q13:T13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="R18:T18"/>
-    <mergeCell ref="R16:T16"/>
     <mergeCell ref="D1:I1"/>
     <mergeCell ref="R21:T21"/>
     <mergeCell ref="B3:K3"/>
@@ -2620,6 +2603,17 @@
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="I6:O6"/>
     <mergeCell ref="Q6:T6"/>
+    <mergeCell ref="R20:T20"/>
+    <mergeCell ref="R17:T17"/>
+    <mergeCell ref="R19:T19"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="Q13:T13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="R18:T18"/>
+    <mergeCell ref="R16:T16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2658,562 +2652,576 @@
   <sheetData>
     <row r="1" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B1" s="8"/>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="28"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="46"/>
     </row>
     <row r="3" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="32"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="52"/>
     </row>
     <row r="5" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B5" s="7"/>
     </row>
     <row r="6" spans="2:30" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="45" t="s">
+      <c r="B6" s="68" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="102" t="s">
+      <c r="C6" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="D6" s="45" t="s">
+      <c r="D6" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="46" t="s">
+      <c r="E6" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="107" t="s">
+      <c r="F6" s="63" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="108"/>
-      <c r="H6" s="108"/>
-      <c r="I6" s="108"/>
-      <c r="J6" s="108"/>
-      <c r="K6" s="108"/>
-      <c r="L6" s="108"/>
-      <c r="M6" s="108"/>
-      <c r="N6" s="108"/>
-      <c r="O6" s="108"/>
-      <c r="P6" s="108"/>
-      <c r="Q6" s="108"/>
-      <c r="R6" s="108"/>
-      <c r="S6" s="108"/>
-      <c r="T6" s="108"/>
-      <c r="U6" s="108"/>
-      <c r="V6" s="108"/>
-      <c r="W6" s="108"/>
-      <c r="X6" s="108"/>
-      <c r="Y6" s="108"/>
-      <c r="Z6" s="108"/>
-      <c r="AA6" s="108"/>
-      <c r="AB6" s="108"/>
-      <c r="AC6" s="108"/>
-      <c r="AD6" s="109"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="64"/>
+      <c r="L6" s="64"/>
+      <c r="M6" s="64"/>
+      <c r="N6" s="64"/>
+      <c r="O6" s="64"/>
+      <c r="P6" s="64"/>
+      <c r="Q6" s="64"/>
+      <c r="R6" s="64"/>
+      <c r="S6" s="64"/>
+      <c r="T6" s="64"/>
+      <c r="U6" s="64"/>
+      <c r="V6" s="64"/>
+      <c r="W6" s="64"/>
+      <c r="X6" s="64"/>
+      <c r="Y6" s="64"/>
+      <c r="Z6" s="64"/>
+      <c r="AA6" s="64"/>
+      <c r="AB6" s="64"/>
+      <c r="AC6" s="64"/>
+      <c r="AD6" s="65"/>
     </row>
     <row r="7" spans="2:30" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="45"/>
-      <c r="C7" s="102"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="53" t="s">
+      <c r="B7" s="68"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="70"/>
+      <c r="F7" s="76" t="s">
         <v>41</v>
       </c>
-      <c r="G7" s="91" t="s">
+      <c r="G7" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="H7" s="105"/>
-      <c r="I7" s="105"/>
-      <c r="J7" s="105"/>
-      <c r="K7" s="105"/>
-      <c r="L7" s="105"/>
-      <c r="M7" s="105"/>
-      <c r="N7" s="105"/>
-      <c r="O7" s="105"/>
-      <c r="P7" s="105"/>
-      <c r="Q7" s="105"/>
-      <c r="R7" s="106"/>
-      <c r="S7" s="49" t="s">
+      <c r="H7" s="77"/>
+      <c r="I7" s="77"/>
+      <c r="J7" s="77"/>
+      <c r="K7" s="77"/>
+      <c r="L7" s="77"/>
+      <c r="M7" s="77"/>
+      <c r="N7" s="77"/>
+      <c r="O7" s="77"/>
+      <c r="P7" s="77"/>
+      <c r="Q7" s="77"/>
+      <c r="R7" s="67"/>
+      <c r="S7" s="75" t="s">
         <v>43</v>
       </c>
-      <c r="T7" s="49"/>
-      <c r="U7" s="49"/>
-      <c r="V7" s="49"/>
-      <c r="W7" s="49"/>
-      <c r="X7" s="48" t="s">
+      <c r="T7" s="75"/>
+      <c r="U7" s="75"/>
+      <c r="V7" s="75"/>
+      <c r="W7" s="75"/>
+      <c r="X7" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="Y7" s="48"/>
-      <c r="Z7" s="48"/>
-      <c r="AA7" s="48"/>
-      <c r="AB7" s="48"/>
-      <c r="AC7" s="48"/>
-      <c r="AD7" s="48"/>
+      <c r="Y7" s="71"/>
+      <c r="Z7" s="71"/>
+      <c r="AA7" s="71"/>
+      <c r="AB7" s="71"/>
+      <c r="AC7" s="71"/>
+      <c r="AD7" s="71"/>
     </row>
     <row r="8" spans="2:30" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="45"/>
-      <c r="C8" s="103"/>
-      <c r="D8" s="50" t="s">
+      <c r="B8" s="68"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="72" t="s">
         <v>94</v>
       </c>
-      <c r="E8" s="50" t="s">
+      <c r="E8" s="72" t="s">
         <v>95</v>
       </c>
-      <c r="F8" s="53"/>
-      <c r="G8" s="52" t="s">
+      <c r="F8" s="76"/>
+      <c r="G8" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52" t="s">
+      <c r="H8" s="74"/>
+      <c r="I8" s="74" t="s">
         <v>97</v>
       </c>
-      <c r="J8" s="52"/>
-      <c r="K8" s="52" t="s">
+      <c r="J8" s="74"/>
+      <c r="K8" s="74" t="s">
         <v>98</v>
       </c>
-      <c r="L8" s="52"/>
-      <c r="M8" s="91" t="s">
+      <c r="L8" s="74"/>
+      <c r="M8" s="66" t="s">
         <v>99</v>
       </c>
-      <c r="N8" s="106"/>
-      <c r="O8" s="91" t="s">
+      <c r="N8" s="67"/>
+      <c r="O8" s="66" t="s">
         <v>100</v>
       </c>
-      <c r="P8" s="106"/>
-      <c r="Q8" s="52" t="s">
+      <c r="P8" s="67"/>
+      <c r="Q8" s="74" t="s">
         <v>101</v>
       </c>
-      <c r="R8" s="52"/>
-      <c r="S8" s="49" t="s">
+      <c r="R8" s="74"/>
+      <c r="S8" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="T8" s="49" t="s">
+      <c r="T8" s="75" t="s">
         <v>35</v>
       </c>
-      <c r="U8" s="49" t="s">
+      <c r="U8" s="75" t="s">
         <v>36</v>
       </c>
-      <c r="V8" s="49" t="s">
+      <c r="V8" s="75" t="s">
         <v>89</v>
       </c>
-      <c r="W8" s="49" t="s">
+      <c r="W8" s="75" t="s">
         <v>91</v>
       </c>
-      <c r="X8" s="48">
+      <c r="X8" s="71">
         <v>0</v>
       </c>
-      <c r="Y8" s="48">
+      <c r="Y8" s="71">
         <v>1</v>
       </c>
-      <c r="Z8" s="48">
+      <c r="Z8" s="71">
         <v>2</v>
       </c>
-      <c r="AA8" s="48" t="s">
+      <c r="AA8" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="AB8" s="48" t="s">
+      <c r="AB8" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="AC8" s="48" t="s">
+      <c r="AC8" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="AD8" s="48" t="s">
+      <c r="AD8" s="71" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9" spans="2:30" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="45"/>
-      <c r="C9" s="104"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="93" t="s">
+      <c r="B9" s="68"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="73"/>
+      <c r="E9" s="73"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="H9" s="93" t="s">
+      <c r="H9" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="I9" s="93" t="s">
+      <c r="I9" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="J9" s="93" t="s">
+      <c r="J9" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="K9" s="93" t="s">
+      <c r="K9" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="L9" s="93" t="s">
+      <c r="L9" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="M9" s="93" t="s">
+      <c r="M9" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="N9" s="93" t="s">
+      <c r="N9" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="O9" s="93" t="s">
+      <c r="O9" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="P9" s="93" t="s">
+      <c r="P9" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="Q9" s="93" t="s">
+      <c r="Q9" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="R9" s="93" t="s">
+      <c r="R9" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="S9" s="49"/>
-      <c r="T9" s="49"/>
-      <c r="U9" s="49"/>
-      <c r="V9" s="49"/>
-      <c r="W9" s="49"/>
-      <c r="X9" s="48"/>
-      <c r="Y9" s="48"/>
-      <c r="Z9" s="48"/>
-      <c r="AA9" s="48"/>
-      <c r="AB9" s="48"/>
-      <c r="AC9" s="48"/>
-      <c r="AD9" s="48"/>
+      <c r="S9" s="75"/>
+      <c r="T9" s="75"/>
+      <c r="U9" s="75"/>
+      <c r="V9" s="75"/>
+      <c r="W9" s="75"/>
+      <c r="X9" s="71"/>
+      <c r="Y9" s="71"/>
+      <c r="Z9" s="71"/>
+      <c r="AA9" s="71"/>
+      <c r="AB9" s="71"/>
+      <c r="AC9" s="71"/>
+      <c r="AD9" s="71"/>
     </row>
     <row r="10" spans="2:30" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B10" s="94" t="s">
+      <c r="B10" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="94" t="s">
+      <c r="C10" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="D10" s="94" t="s">
+      <c r="D10" s="31" t="s">
         <v>103</v>
       </c>
-      <c r="E10" s="95" t="s">
+      <c r="E10" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="F10" s="96" t="s">
+      <c r="F10" s="33" t="s">
         <v>105</v>
       </c>
-      <c r="G10" s="97" t="s">
-        <v>106</v>
-      </c>
-      <c r="H10" s="97"/>
-      <c r="I10" s="97"/>
-      <c r="J10" s="97"/>
-      <c r="K10" s="97"/>
-      <c r="L10" s="97"/>
-      <c r="M10" s="97"/>
-      <c r="N10" s="97"/>
-      <c r="O10" s="97"/>
-      <c r="P10" s="97"/>
-      <c r="Q10" s="97"/>
-      <c r="R10" s="97"/>
-      <c r="S10" s="98" t="s">
-        <v>106</v>
-      </c>
-      <c r="T10" s="98"/>
-      <c r="U10" s="98"/>
-      <c r="V10" s="98"/>
-      <c r="W10" s="98"/>
-      <c r="X10" s="99" t="s">
-        <v>106</v>
-      </c>
-      <c r="Y10" s="99"/>
-      <c r="Z10" s="99"/>
-      <c r="AA10" s="99"/>
-      <c r="AB10" s="99"/>
-      <c r="AC10" s="99"/>
-      <c r="AD10" s="99" t="s">
+      <c r="G10" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="H10" s="34"/>
+      <c r="I10" s="34"/>
+      <c r="J10" s="34"/>
+      <c r="K10" s="34"/>
+      <c r="L10" s="34"/>
+      <c r="M10" s="34"/>
+      <c r="N10" s="34"/>
+      <c r="O10" s="34"/>
+      <c r="P10" s="34"/>
+      <c r="Q10" s="34"/>
+      <c r="R10" s="34"/>
+      <c r="S10" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="T10" s="35"/>
+      <c r="U10" s="35"/>
+      <c r="V10" s="35"/>
+      <c r="W10" s="35"/>
+      <c r="X10" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y10" s="36"/>
+      <c r="Z10" s="36"/>
+      <c r="AA10" s="36"/>
+      <c r="AB10" s="36"/>
+      <c r="AC10" s="36"/>
+      <c r="AD10" s="36" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="11" spans="2:30" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="B11" s="94" t="s">
+      <c r="B11" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="94" t="s">
+      <c r="C11" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="D11" s="94" t="s">
+      <c r="D11" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="E11" s="95" t="s">
+      <c r="E11" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="F11" s="96" t="s">
+      <c r="F11" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="G11" s="97"/>
-      <c r="H11" s="97" t="s">
-        <v>106</v>
-      </c>
-      <c r="I11" s="97" t="s">
-        <v>106</v>
-      </c>
-      <c r="J11" s="97"/>
-      <c r="K11" s="97" t="s">
-        <v>106</v>
-      </c>
-      <c r="L11" s="97"/>
-      <c r="M11" s="97" t="s">
-        <v>106</v>
-      </c>
-      <c r="N11" s="97"/>
-      <c r="O11" s="97"/>
-      <c r="P11" s="97" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q11" s="97"/>
-      <c r="R11" s="97" t="s">
-        <v>106</v>
-      </c>
-      <c r="S11" s="98"/>
-      <c r="T11" s="98"/>
-      <c r="U11" s="98"/>
-      <c r="V11" s="98"/>
-      <c r="W11" s="98" t="s">
-        <v>106</v>
-      </c>
-      <c r="X11" s="99" t="s">
-        <v>106</v>
-      </c>
-      <c r="Y11" s="99"/>
-      <c r="Z11" s="99"/>
-      <c r="AA11" s="99"/>
-      <c r="AB11" s="99"/>
-      <c r="AC11" s="99"/>
-      <c r="AD11" s="99" t="s">
+      <c r="G11" s="34"/>
+      <c r="H11" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="I11" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="J11" s="34"/>
+      <c r="K11" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="L11" s="34"/>
+      <c r="M11" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="N11" s="34"/>
+      <c r="O11" s="34"/>
+      <c r="P11" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q11" s="34"/>
+      <c r="R11" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="S11" s="35"/>
+      <c r="T11" s="35"/>
+      <c r="U11" s="35"/>
+      <c r="V11" s="35"/>
+      <c r="W11" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="X11" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y11" s="36"/>
+      <c r="Z11" s="36"/>
+      <c r="AA11" s="36"/>
+      <c r="AB11" s="36"/>
+      <c r="AC11" s="36"/>
+      <c r="AD11" s="36" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="12" spans="2:30" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="B12" s="94" t="s">
+      <c r="B12" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="C12" s="94" t="s">
+      <c r="C12" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="D12" s="100" t="s">
+      <c r="D12" s="37" t="s">
         <v>110</v>
       </c>
-      <c r="E12" s="101" t="s">
+      <c r="E12" s="38" t="s">
         <v>104</v>
       </c>
-      <c r="F12" s="96" t="s">
+      <c r="F12" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="G12" s="97"/>
-      <c r="H12" s="97" t="s">
-        <v>106</v>
-      </c>
-      <c r="I12" s="97"/>
-      <c r="J12" s="97" t="s">
-        <v>106</v>
-      </c>
-      <c r="K12" s="97"/>
-      <c r="L12" s="97" t="s">
-        <v>106</v>
-      </c>
-      <c r="M12" s="97"/>
-      <c r="N12" s="97" t="s">
-        <v>106</v>
-      </c>
-      <c r="O12" s="97"/>
-      <c r="P12" s="97" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q12" s="97"/>
-      <c r="R12" s="97" t="s">
-        <v>106</v>
-      </c>
-      <c r="S12" s="98"/>
-      <c r="T12" s="98" t="s">
-        <v>106</v>
-      </c>
-      <c r="U12" s="98"/>
-      <c r="V12" s="98"/>
-      <c r="W12" s="98"/>
-      <c r="X12" s="99"/>
-      <c r="Y12" s="99" t="s">
-        <v>106</v>
-      </c>
-      <c r="Z12" s="99"/>
-      <c r="AA12" s="99"/>
-      <c r="AB12" s="99" t="s">
-        <v>106</v>
-      </c>
-      <c r="AC12" s="99"/>
-      <c r="AD12" s="99"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="I12" s="34"/>
+      <c r="J12" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="K12" s="34"/>
+      <c r="L12" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="M12" s="34"/>
+      <c r="N12" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="O12" s="34"/>
+      <c r="P12" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q12" s="34"/>
+      <c r="R12" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="S12" s="35"/>
+      <c r="T12" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="U12" s="35"/>
+      <c r="V12" s="35"/>
+      <c r="W12" s="35"/>
+      <c r="X12" s="36"/>
+      <c r="Y12" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="Z12" s="36"/>
+      <c r="AA12" s="36"/>
+      <c r="AB12" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="AC12" s="36"/>
+      <c r="AD12" s="36"/>
     </row>
     <row r="13" spans="2:30" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="B13" s="94" t="s">
+      <c r="B13" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="C13" s="94" t="s">
+      <c r="C13" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="D13" s="100" t="s">
+      <c r="D13" s="37" t="s">
         <v>110</v>
       </c>
-      <c r="E13" s="95" t="s">
+      <c r="E13" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="F13" s="96" t="s">
+      <c r="F13" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="G13" s="97"/>
-      <c r="H13" s="97" t="s">
-        <v>106</v>
-      </c>
-      <c r="I13" s="97"/>
-      <c r="J13" s="97" t="s">
-        <v>106</v>
-      </c>
-      <c r="K13" s="97"/>
-      <c r="L13" s="97"/>
-      <c r="M13" s="97"/>
-      <c r="N13" s="97"/>
-      <c r="O13" s="97"/>
-      <c r="P13" s="97"/>
-      <c r="Q13" s="97" t="s">
-        <v>106</v>
-      </c>
-      <c r="R13" s="97"/>
-      <c r="S13" s="98"/>
-      <c r="T13" s="98"/>
-      <c r="U13" s="98"/>
-      <c r="V13" s="98" t="s">
-        <v>106</v>
-      </c>
-      <c r="W13" s="98"/>
-      <c r="X13" s="99" t="s">
-        <v>106</v>
-      </c>
-      <c r="Y13" s="99"/>
-      <c r="Z13" s="99"/>
-      <c r="AA13" s="99"/>
-      <c r="AB13" s="99"/>
-      <c r="AC13" s="99"/>
-      <c r="AD13" s="99"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="I13" s="34"/>
+      <c r="J13" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="K13" s="34"/>
+      <c r="L13" s="34"/>
+      <c r="M13" s="34"/>
+      <c r="N13" s="34"/>
+      <c r="O13" s="34"/>
+      <c r="P13" s="34"/>
+      <c r="Q13" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="R13" s="34"/>
+      <c r="S13" s="35"/>
+      <c r="T13" s="35"/>
+      <c r="U13" s="35"/>
+      <c r="V13" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="W13" s="35"/>
+      <c r="X13" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y13" s="36"/>
+      <c r="Z13" s="36"/>
+      <c r="AA13" s="36"/>
+      <c r="AB13" s="36"/>
+      <c r="AC13" s="36"/>
+      <c r="AD13" s="36"/>
     </row>
     <row r="14" spans="2:30" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="B14" s="94" t="s">
+      <c r="B14" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="C14" s="94" t="s">
+      <c r="C14" s="31" t="s">
         <v>116</v>
       </c>
-      <c r="D14" s="94" t="s">
+      <c r="D14" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="E14" s="95" t="s">
+      <c r="E14" s="32" t="s">
         <v>118</v>
       </c>
-      <c r="F14" s="96" t="s">
+      <c r="F14" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="G14" s="97"/>
-      <c r="H14" s="97"/>
-      <c r="I14" s="97"/>
-      <c r="J14" s="97"/>
-      <c r="K14" s="97" t="s">
-        <v>106</v>
-      </c>
-      <c r="L14" s="97"/>
-      <c r="M14" s="97"/>
-      <c r="N14" s="97" t="s">
-        <v>106</v>
-      </c>
-      <c r="O14" s="97" t="s">
-        <v>106</v>
-      </c>
-      <c r="P14" s="97"/>
-      <c r="Q14" s="97"/>
-      <c r="R14" s="97"/>
-      <c r="S14" s="98"/>
-      <c r="T14" s="98" t="s">
-        <v>106</v>
-      </c>
-      <c r="U14" s="98"/>
-      <c r="V14" s="98"/>
-      <c r="W14" s="98"/>
-      <c r="X14" s="99"/>
-      <c r="Y14" s="99"/>
-      <c r="Z14" s="99" t="s">
-        <v>106</v>
-      </c>
-      <c r="AA14" s="99"/>
-      <c r="AB14" s="99" t="s">
-        <v>106</v>
-      </c>
-      <c r="AC14" s="99"/>
-      <c r="AD14" s="99"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="34"/>
+      <c r="I14" s="34"/>
+      <c r="J14" s="34"/>
+      <c r="K14" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="L14" s="34"/>
+      <c r="M14" s="34"/>
+      <c r="N14" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="O14" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="P14" s="34"/>
+      <c r="Q14" s="34"/>
+      <c r="R14" s="34"/>
+      <c r="S14" s="35"/>
+      <c r="T14" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="U14" s="35"/>
+      <c r="V14" s="35"/>
+      <c r="W14" s="35"/>
+      <c r="X14" s="36"/>
+      <c r="Y14" s="36"/>
+      <c r="Z14" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="AA14" s="36"/>
+      <c r="AB14" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="AC14" s="36"/>
+      <c r="AD14" s="36"/>
     </row>
     <row r="15" spans="2:30" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="B15" s="94" t="s">
+      <c r="B15" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="C15" s="94" t="s">
+      <c r="C15" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="D15" s="94" t="s">
+      <c r="D15" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="E15" s="95" t="s">
+      <c r="E15" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="F15" s="96" t="s">
+      <c r="F15" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="G15" s="97"/>
-      <c r="H15" s="97" t="s">
-        <v>106</v>
-      </c>
-      <c r="I15" s="97"/>
-      <c r="J15" s="97" t="s">
-        <v>106</v>
-      </c>
-      <c r="K15" s="97"/>
-      <c r="L15" s="97" t="s">
-        <v>106</v>
-      </c>
-      <c r="M15" s="97"/>
-      <c r="N15" s="97" t="s">
-        <v>106</v>
-      </c>
-      <c r="O15" s="97"/>
-      <c r="P15" s="97" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q15" s="97"/>
-      <c r="R15" s="97"/>
-      <c r="S15" s="98"/>
-      <c r="T15" s="98"/>
-      <c r="U15" s="98" t="s">
-        <v>106</v>
-      </c>
-      <c r="V15" s="98"/>
-      <c r="W15" s="98"/>
-      <c r="X15" s="99" t="s">
-        <v>106</v>
-      </c>
-      <c r="Y15" s="99"/>
-      <c r="Z15" s="99"/>
-      <c r="AA15" s="99"/>
-      <c r="AB15" s="99"/>
-      <c r="AC15" s="99"/>
-      <c r="AD15" s="99"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="35"/>
+      <c r="T15" s="35"/>
+      <c r="U15" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="V15" s="35"/>
+      <c r="W15" s="35"/>
+      <c r="X15" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y15" s="36"/>
+      <c r="Z15" s="36"/>
+      <c r="AA15" s="36"/>
+      <c r="AB15" s="36"/>
+      <c r="AC15" s="36"/>
+      <c r="AD15" s="36"/>
     </row>
     <row r="16" spans="2:30" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B16" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="F7:F9"/>
+    <mergeCell ref="S7:W7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="Q8:R8"/>
+    <mergeCell ref="G7:R7"/>
     <mergeCell ref="F6:AD6"/>
     <mergeCell ref="M8:N8"/>
     <mergeCell ref="O8:P8"/>
@@ -3230,20 +3238,6 @@
     <mergeCell ref="W8:W9"/>
     <mergeCell ref="X7:AD7"/>
     <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="F7:F9"/>
-    <mergeCell ref="S7:W7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="Q8:R8"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="G7:R7"/>
-    <mergeCell ref="D1:G1"/>
-    <mergeCell ref="B3:F3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3273,192 +3267,192 @@
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B1" s="8"/>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="28"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="46"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="78" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
-      <c r="L3" s="56"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
+      <c r="K3" s="78"/>
+      <c r="L3" s="78"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B4" s="57" t="s">
+      <c r="B4" s="79" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="66" t="s">
+      <c r="C4" s="86" t="s">
         <v>55</v>
       </c>
-      <c r="D4" s="68" t="s">
+      <c r="D4" s="88" t="s">
         <v>56</v>
       </c>
-      <c r="E4" s="59" t="s">
+      <c r="E4" s="81" t="s">
         <v>57</v>
       </c>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="59" t="s">
+      <c r="F4" s="85"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="81" t="s">
         <v>58</v>
       </c>
-      <c r="L4" s="60"/>
+      <c r="L4" s="82"/>
     </row>
     <row r="5" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="58"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="61" t="s">
+      <c r="B5" s="80"/>
+      <c r="C5" s="87"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="90" t="s">
         <v>94</v>
       </c>
-      <c r="F5" s="110"/>
-      <c r="G5" s="110"/>
-      <c r="H5" s="110"/>
-      <c r="I5" s="110"/>
-      <c r="J5" s="62"/>
-      <c r="K5" s="111" t="s">
+      <c r="F5" s="91"/>
+      <c r="G5" s="91"/>
+      <c r="H5" s="91"/>
+      <c r="I5" s="91"/>
+      <c r="J5" s="92"/>
+      <c r="K5" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="L5" s="111" t="s">
+      <c r="L5" s="39" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="6" spans="2:14" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="115">
+      <c r="B6" s="41">
         <v>9</v>
       </c>
-      <c r="C6" s="63" t="s">
+      <c r="C6" s="83" t="s">
         <v>61</v>
       </c>
-      <c r="D6" s="112" t="s">
+      <c r="D6" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="E6" s="118" t="s">
+      <c r="E6" s="93" t="s">
         <v>123</v>
       </c>
-      <c r="F6" s="119"/>
-      <c r="G6" s="119"/>
-      <c r="H6" s="119"/>
-      <c r="I6" s="119"/>
-      <c r="J6" s="120"/>
-      <c r="K6" s="114" t="s">
+      <c r="F6" s="94"/>
+      <c r="G6" s="94"/>
+      <c r="H6" s="94"/>
+      <c r="I6" s="94"/>
+      <c r="J6" s="95"/>
+      <c r="K6" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="L6" s="115" t="s">
+      <c r="L6" s="41" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="2:14" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="B7" s="115">
+    <row r="7" spans="2:14" ht="78" x14ac:dyDescent="0.3">
+      <c r="B7" s="41">
         <v>10</v>
       </c>
-      <c r="C7" s="63"/>
-      <c r="D7" s="112" t="s">
+      <c r="C7" s="83"/>
+      <c r="D7" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="E7" s="59" t="s">
+      <c r="E7" s="81" t="s">
         <v>129</v>
       </c>
-      <c r="F7" s="65"/>
-      <c r="G7" s="65"/>
-      <c r="H7" s="65"/>
-      <c r="I7" s="65"/>
-      <c r="J7" s="60"/>
-      <c r="K7" s="114" t="s">
+      <c r="F7" s="85"/>
+      <c r="G7" s="85"/>
+      <c r="H7" s="85"/>
+      <c r="I7" s="85"/>
+      <c r="J7" s="82"/>
+      <c r="K7" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="L7" s="114" t="s">
+      <c r="L7" s="32" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="8" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B8" s="115">
+      <c r="B8" s="41">
         <v>11</v>
       </c>
-      <c r="C8" s="63"/>
-      <c r="D8" s="112" t="s">
+      <c r="C8" s="83"/>
+      <c r="D8" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="E8" s="59" t="s">
+      <c r="E8" s="81" t="s">
         <v>125</v>
       </c>
-      <c r="F8" s="65"/>
-      <c r="G8" s="65"/>
-      <c r="H8" s="65"/>
-      <c r="I8" s="65"/>
-      <c r="J8" s="60"/>
-      <c r="K8" s="114" t="s">
+      <c r="F8" s="85"/>
+      <c r="G8" s="85"/>
+      <c r="H8" s="85"/>
+      <c r="I8" s="85"/>
+      <c r="J8" s="82"/>
+      <c r="K8" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="L8" s="115" t="s">
+      <c r="L8" s="41" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="9" spans="2:14" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="B9" s="115">
+      <c r="B9" s="41">
         <v>12</v>
       </c>
-      <c r="C9" s="63"/>
-      <c r="D9" s="112" t="s">
+      <c r="C9" s="83"/>
+      <c r="D9" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="E9" s="59" t="s">
+      <c r="E9" s="81" t="s">
         <v>125</v>
       </c>
-      <c r="F9" s="65"/>
-      <c r="G9" s="65"/>
-      <c r="H9" s="65"/>
-      <c r="I9" s="65"/>
-      <c r="J9" s="60"/>
-      <c r="K9" s="114" t="s">
+      <c r="F9" s="85"/>
+      <c r="G9" s="85"/>
+      <c r="H9" s="85"/>
+      <c r="I9" s="85"/>
+      <c r="J9" s="82"/>
+      <c r="K9" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="L9" s="115" t="s">
+      <c r="L9" s="41" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="10" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="111">
+      <c r="B10" s="39">
         <v>13</v>
       </c>
-      <c r="C10" s="64"/>
-      <c r="D10" s="113" t="s">
+      <c r="C10" s="84"/>
+      <c r="D10" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="111" t="s">
+      <c r="E10" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="111" t="s">
+      <c r="F10" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="111" t="s">
+      <c r="G10" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="H10" s="111" t="s">
+      <c r="H10" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="I10" s="116" t="s">
+      <c r="I10" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="J10" s="117"/>
-      <c r="K10" s="111" t="s">
+      <c r="J10" s="43"/>
+      <c r="K10" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="L10" s="111" t="s">
+      <c r="L10" s="39" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3482,97 +3476,100 @@
       <c r="K12" s="10"/>
     </row>
     <row r="13" spans="2:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="70" t="s">
+      <c r="B13" s="111" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="71"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="71"/>
-      <c r="F13" s="72" t="s">
+      <c r="C13" s="112"/>
+      <c r="D13" s="112"/>
+      <c r="E13" s="112"/>
+      <c r="F13" s="104" t="s">
         <v>65</v>
       </c>
-      <c r="G13" s="73"/>
-      <c r="H13" s="70" t="s">
+      <c r="G13" s="105"/>
+      <c r="H13" s="111" t="s">
         <v>66</v>
       </c>
-      <c r="I13" s="71"/>
-      <c r="J13" s="71"/>
-      <c r="K13" s="71"/>
-      <c r="L13" s="87"/>
-      <c r="M13" s="54" t="s">
+      <c r="I13" s="112"/>
+      <c r="J13" s="112"/>
+      <c r="K13" s="112"/>
+      <c r="L13" s="113"/>
+      <c r="M13" s="117" t="s">
         <v>67</v>
       </c>
-      <c r="N13" s="55"/>
+      <c r="N13" s="118"/>
     </row>
     <row r="14" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="82" t="s">
+      <c r="B14" s="96" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="78" t="s">
+      <c r="C14" s="98" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="78" t="s">
+      <c r="D14" s="98" t="s">
         <v>70</v>
       </c>
-      <c r="E14" s="84" t="s">
+      <c r="E14" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="F14" s="75" t="s">
+      <c r="F14" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="G14" s="74" t="s">
+      <c r="G14" s="106" t="s">
         <v>73</v>
       </c>
-      <c r="H14" s="76" t="s">
+      <c r="H14" s="107" t="s">
         <v>74</v>
       </c>
-      <c r="I14" s="78" t="s">
+      <c r="I14" s="98" t="s">
         <v>68</v>
       </c>
-      <c r="J14" s="78" t="s">
+      <c r="J14" s="98" t="s">
         <v>69</v>
       </c>
-      <c r="K14" s="80" t="s">
+      <c r="K14" s="109" t="s">
         <v>75</v>
       </c>
-      <c r="L14" s="88" t="s">
+      <c r="L14" s="114" t="s">
         <v>76</v>
       </c>
-      <c r="M14" s="90" t="s">
+      <c r="M14" s="116" t="s">
         <v>77</v>
       </c>
-      <c r="N14" s="66" t="s">
+      <c r="N14" s="86" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B15" s="83"/>
-      <c r="C15" s="79"/>
-      <c r="D15" s="79"/>
-      <c r="E15" s="85"/>
-      <c r="F15" s="86"/>
-      <c r="G15" s="74"/>
-      <c r="H15" s="77"/>
-      <c r="I15" s="79"/>
-      <c r="J15" s="79"/>
-      <c r="K15" s="81"/>
-      <c r="L15" s="89"/>
-      <c r="M15" s="82"/>
-      <c r="N15" s="75"/>
+      <c r="B15" s="97"/>
+      <c r="C15" s="99"/>
+      <c r="D15" s="99"/>
+      <c r="E15" s="101"/>
+      <c r="F15" s="103"/>
+      <c r="G15" s="106"/>
+      <c r="H15" s="108"/>
+      <c r="I15" s="99"/>
+      <c r="J15" s="99"/>
+      <c r="K15" s="110"/>
+      <c r="L15" s="115"/>
+      <c r="M15" s="96"/>
+      <c r="N15" s="102"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B16" s="14">
-        <f>SUM(C16:D16)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C16" s="11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D16" s="11">
         <v>0</v>
       </c>
-      <c r="E16" s="12"/>
-      <c r="F16" s="13"/>
+      <c r="E16" s="12">
+        <v>100</v>
+      </c>
+      <c r="F16" s="13">
+        <v>0</v>
+      </c>
       <c r="G16" s="6" t="s">
         <v>79</v>
       </c>
@@ -3580,7 +3577,6 @@
         <v>79</v>
       </c>
       <c r="I16" s="14">
-        <f>SUM(J16:K16)</f>
         <v>0</v>
       </c>
       <c r="J16" s="11">
@@ -3589,17 +3585,36 @@
       <c r="K16" s="15">
         <v>0</v>
       </c>
-      <c r="L16" s="16"/>
+      <c r="L16" s="16">
+        <v>100</v>
+      </c>
       <c r="M16" s="4" t="s">
         <v>79</v>
       </c>
       <c r="N16" s="17">
-        <f>C16</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="H13:L13"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
     <mergeCell ref="B3:L3"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="K4:L4"/>
@@ -3612,24 +3627,6 @@
     <mergeCell ref="E7:J7"/>
     <mergeCell ref="E8:J8"/>
     <mergeCell ref="E9:J9"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="D1:G1"/>
-    <mergeCell ref="B13:E13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3637,9 +3634,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3811,19 +3811,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6597AB9C-DC10-4824-8900-518D3B18165A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5426D20B-58AE-4BE9-8733-DFB2BC19D8C6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3847,9 +3843,10 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5426D20B-58AE-4BE9-8733-DFB2BC19D8C6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6597AB9C-DC10-4824-8900-518D3B18165A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Docs/Lab03/Lab03_WBT_TCs_Form.xlsx
+++ b/Docs/Lab03/Lab03_WBT_TCs_Form.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F612B6DA-1AE8-403D-B809-5218114D6DBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{962BA179-A934-4C94-8E32-4DCE28808404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2700" yWindow="-16320" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="128">
   <si>
     <t>VVSS, Info Romana, 2024-2025</t>
   </si>
@@ -230,9 +230,6 @@
   </si>
   <si>
     <t>F02_TC01</t>
-  </si>
-  <si>
-    <t>F01_TC02</t>
   </si>
   <si>
     <t>WBT Implemented TCs</t>
@@ -529,9 +526,6 @@
     <t>p.getName().contains(searchItem)</t>
   </si>
   <si>
-    <t xml:space="preserve"> (p.getProductId()+"").equals(searchItem)</t>
-  </si>
-  <si>
     <t>!isFound</t>
   </si>
   <si>
@@ -553,9 +547,6 @@
     <t>44, 46, 47, 48, 49, 56</t>
   </si>
   <si>
-    <t>F01_TC03</t>
-  </si>
-  <si>
     <t>"produs"</t>
   </si>
   <si>
@@ -565,18 +556,12 @@
     <t>44, 46, 47, 48, 50, 52, 53, 56</t>
   </si>
   <si>
-    <t>F01_TC04</t>
-  </si>
-  <si>
     <t>(0, null, 0.0, 0, 0, 0, null)</t>
   </si>
   <si>
     <t>44, 46, 47, 52, 53, 56</t>
   </si>
   <si>
-    <t>F01_TC05</t>
-  </si>
-  <si>
     <t>"a","b"</t>
   </si>
   <si>
@@ -584,9 +569,6 @@
   </si>
   <si>
     <t>(1, "b", 7.45, 7, 2, 20, 1:2:3)</t>
-  </si>
-  <si>
-    <t>F01_TC06</t>
   </si>
   <si>
     <t>44, 46, 47, 52, 55, 56</t>
@@ -618,6 +600,18 @@
   </si>
   <si>
     <t>"itemName", items.txt</t>
+  </si>
+  <si>
+    <t>(p.getProductId()+"").equals(searchItem)</t>
+  </si>
+  <si>
+    <t>F02_TC05</t>
+  </si>
+  <si>
+    <t>F02_TC06</t>
+  </si>
+  <si>
+    <t>"TEST", null</t>
   </si>
 </sst>
 </file>
@@ -1458,51 +1452,78 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1512,12 +1533,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1527,25 +1542,76 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1572,9 +1638,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1600,75 +1663,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1695,13 +1689,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>567690</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>93980</xdr:rowOff>
+      <xdr:rowOff>97790</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>592241</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>23652</xdr:rowOff>
+      <xdr:colOff>588431</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>46144</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1724,8 +1718,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="567690" y="1211580"/>
-          <a:ext cx="4367951" cy="1792339"/>
+          <a:off x="567690" y="1177290"/>
+          <a:ext cx="4391658" cy="2467187"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2152,7 +2146,7 @@
         <v>9</v>
       </c>
       <c r="O7" s="14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P7" s="14">
         <v>233</v>
@@ -2167,7 +2161,7 @@
         <v>10</v>
       </c>
       <c r="O8" s="14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P8" s="14">
         <v>233</v>
@@ -2184,7 +2178,7 @@
         <v>12</v>
       </c>
       <c r="O9" s="14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P9" s="14">
         <v>233</v>
@@ -2200,7 +2194,7 @@
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -2251,18 +2245,18 @@
       <c r="I1" s="46"/>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="50"/>
     </row>
     <row r="6" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B6" s="44" t="s">
@@ -2303,11 +2297,11 @@
       <c r="I8" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="Q8" s="49" t="s">
+      <c r="Q8" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="R8" s="49"/>
-      <c r="S8" s="49"/>
+      <c r="R8" s="61"/>
+      <c r="S8" s="61"/>
       <c r="T8" s="21">
         <v>5</v>
       </c>
@@ -2316,110 +2310,110 @@
       <c r="B9" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="48" t="s">
+      <c r="C9" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
       <c r="F9" s="23"/>
       <c r="G9" s="23"/>
       <c r="I9" s="24"/>
-      <c r="Q9" s="49" t="s">
+      <c r="Q9" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="R9" s="49"/>
-      <c r="S9" s="49"/>
+      <c r="R9" s="61"/>
+      <c r="S9" s="61"/>
       <c r="T9" s="21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B10" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="48" t="s">
+      <c r="C10" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="48"/>
-      <c r="E10" s="48"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
       <c r="F10" s="23"/>
       <c r="G10" s="23"/>
-      <c r="I10" s="53" t="e" vm="1">
+      <c r="I10" s="52" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="J10" s="54"/>
-      <c r="K10" s="54"/>
-      <c r="L10" s="54"/>
-      <c r="M10" s="54"/>
-      <c r="N10" s="54"/>
-      <c r="O10" s="55"/>
-      <c r="Q10" s="49" t="s">
+      <c r="J10" s="53"/>
+      <c r="K10" s="53"/>
+      <c r="L10" s="53"/>
+      <c r="M10" s="53"/>
+      <c r="N10" s="53"/>
+      <c r="O10" s="54"/>
+      <c r="Q10" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="R10" s="49" t="s">
+      <c r="R10" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="S10" s="49"/>
+      <c r="S10" s="61"/>
       <c r="T10" s="21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B11" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="48" t="s">
+      <c r="C11" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="48"/>
-      <c r="E11" s="48"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
       <c r="F11" s="23"/>
       <c r="G11" s="23"/>
-      <c r="I11" s="56"/>
-      <c r="J11" s="57"/>
-      <c r="K11" s="57"/>
-      <c r="L11" s="57"/>
-      <c r="M11" s="57"/>
-      <c r="N11" s="57"/>
-      <c r="O11" s="58"/>
+      <c r="I11" s="55"/>
+      <c r="J11" s="56"/>
+      <c r="K11" s="56"/>
+      <c r="L11" s="56"/>
+      <c r="M11" s="56"/>
+      <c r="N11" s="56"/>
+      <c r="O11" s="57"/>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B12" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="48" t="s">
+      <c r="C12" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="48"/>
-      <c r="E12" s="48"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
       <c r="F12" s="23"/>
       <c r="G12" s="23"/>
-      <c r="I12" s="56"/>
-      <c r="J12" s="57"/>
-      <c r="K12" s="57"/>
-      <c r="L12" s="57"/>
-      <c r="M12" s="57"/>
-      <c r="N12" s="57"/>
-      <c r="O12" s="58"/>
+      <c r="I12" s="55"/>
+      <c r="J12" s="56"/>
+      <c r="K12" s="56"/>
+      <c r="L12" s="56"/>
+      <c r="M12" s="56"/>
+      <c r="N12" s="56"/>
+      <c r="O12" s="57"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B13" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="48" t="s">
+      <c r="C13" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="48"/>
-      <c r="E13" s="48"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
       <c r="F13" s="23"/>
       <c r="G13" s="23"/>
-      <c r="I13" s="56"/>
-      <c r="J13" s="57"/>
-      <c r="K13" s="57"/>
-      <c r="L13" s="57"/>
-      <c r="M13" s="57"/>
-      <c r="N13" s="57"/>
-      <c r="O13" s="58"/>
+      <c r="I13" s="55"/>
+      <c r="J13" s="56"/>
+      <c r="K13" s="56"/>
+      <c r="L13" s="56"/>
+      <c r="M13" s="56"/>
+      <c r="N13" s="56"/>
+      <c r="O13" s="57"/>
       <c r="Q13" s="44" t="s">
         <v>31</v>
       </c>
@@ -2431,29 +2425,29 @@
       <c r="B14" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="48" t="s">
+      <c r="C14" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
       <c r="F14" s="23"/>
       <c r="G14" s="23"/>
-      <c r="I14" s="56"/>
-      <c r="J14" s="57"/>
-      <c r="K14" s="57"/>
-      <c r="L14" s="57"/>
-      <c r="M14" s="57"/>
-      <c r="N14" s="57"/>
-      <c r="O14" s="58"/>
+      <c r="I14" s="55"/>
+      <c r="J14" s="56"/>
+      <c r="K14" s="56"/>
+      <c r="L14" s="56"/>
+      <c r="M14" s="56"/>
+      <c r="N14" s="56"/>
+      <c r="O14" s="57"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I15" s="56"/>
-      <c r="J15" s="57"/>
-      <c r="K15" s="57"/>
-      <c r="L15" s="57"/>
-      <c r="M15" s="57"/>
-      <c r="N15" s="57"/>
-      <c r="O15" s="58"/>
+      <c r="I15" s="55"/>
+      <c r="J15" s="56"/>
+      <c r="K15" s="56"/>
+      <c r="L15" s="56"/>
+      <c r="M15" s="56"/>
+      <c r="N15" s="56"/>
+      <c r="O15" s="57"/>
       <c r="Q15" s="19" t="s">
         <v>32</v>
       </c>
@@ -2464,132 +2458,140 @@
       <c r="T15" s="62"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I16" s="56"/>
-      <c r="J16" s="57"/>
-      <c r="K16" s="57"/>
-      <c r="L16" s="57"/>
-      <c r="M16" s="57"/>
-      <c r="N16" s="57"/>
-      <c r="O16" s="58"/>
+      <c r="I16" s="55"/>
+      <c r="J16" s="56"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="56"/>
+      <c r="M16" s="56"/>
+      <c r="N16" s="56"/>
+      <c r="O16" s="57"/>
       <c r="Q16" s="22" t="s">
         <v>34</v>
       </c>
       <c r="R16" s="47" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="S16" s="47"/>
       <c r="T16" s="47"/>
     </row>
     <row r="17" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I17" s="56"/>
-      <c r="J17" s="57"/>
-      <c r="K17" s="57"/>
-      <c r="L17" s="57"/>
-      <c r="M17" s="57"/>
-      <c r="N17" s="57"/>
-      <c r="O17" s="58"/>
+      <c r="I17" s="55"/>
+      <c r="J17" s="56"/>
+      <c r="K17" s="56"/>
+      <c r="L17" s="56"/>
+      <c r="M17" s="56"/>
+      <c r="N17" s="56"/>
+      <c r="O17" s="57"/>
       <c r="Q17" s="22" t="s">
         <v>35</v>
       </c>
       <c r="R17" s="47" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="S17" s="47"/>
       <c r="T17" s="47"/>
     </row>
     <row r="18" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I18" s="56"/>
-      <c r="J18" s="57"/>
-      <c r="K18" s="57"/>
-      <c r="L18" s="57"/>
-      <c r="M18" s="57"/>
-      <c r="N18" s="57"/>
-      <c r="O18" s="58"/>
+      <c r="I18" s="55"/>
+      <c r="J18" s="56"/>
+      <c r="K18" s="56"/>
+      <c r="L18" s="56"/>
+      <c r="M18" s="56"/>
+      <c r="N18" s="56"/>
+      <c r="O18" s="57"/>
       <c r="Q18" s="22" t="s">
         <v>36</v>
       </c>
       <c r="R18" s="47" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="S18" s="47"/>
       <c r="T18" s="47"/>
     </row>
     <row r="19" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I19" s="56"/>
-      <c r="J19" s="57"/>
-      <c r="K19" s="57"/>
-      <c r="L19" s="57"/>
-      <c r="M19" s="57"/>
-      <c r="N19" s="57"/>
-      <c r="O19" s="58"/>
+      <c r="I19" s="55"/>
+      <c r="J19" s="56"/>
+      <c r="K19" s="56"/>
+      <c r="L19" s="56"/>
+      <c r="M19" s="56"/>
+      <c r="N19" s="56"/>
+      <c r="O19" s="57"/>
       <c r="Q19" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="R19" s="47" t="s">
         <v>89</v>
-      </c>
-      <c r="R19" s="47" t="s">
-        <v>90</v>
       </c>
       <c r="S19" s="47"/>
       <c r="T19" s="47"/>
     </row>
     <row r="20" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I20" s="56"/>
-      <c r="J20" s="57"/>
-      <c r="K20" s="57"/>
-      <c r="L20" s="57"/>
-      <c r="M20" s="57"/>
-      <c r="N20" s="57"/>
-      <c r="O20" s="58"/>
+      <c r="I20" s="55"/>
+      <c r="J20" s="56"/>
+      <c r="K20" s="56"/>
+      <c r="L20" s="56"/>
+      <c r="M20" s="56"/>
+      <c r="N20" s="56"/>
+      <c r="O20" s="57"/>
       <c r="Q20" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="R20" s="47" t="s">
         <v>91</v>
-      </c>
-      <c r="R20" s="47" t="s">
-        <v>92</v>
       </c>
       <c r="S20" s="47"/>
       <c r="T20" s="47"/>
     </row>
     <row r="21" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I21" s="56"/>
-      <c r="J21" s="57"/>
-      <c r="K21" s="57"/>
-      <c r="L21" s="57"/>
-      <c r="M21" s="57"/>
-      <c r="N21" s="57"/>
-      <c r="O21" s="58"/>
+      <c r="I21" s="55"/>
+      <c r="J21" s="56"/>
+      <c r="K21" s="56"/>
+      <c r="L21" s="56"/>
+      <c r="M21" s="56"/>
+      <c r="N21" s="56"/>
+      <c r="O21" s="57"/>
       <c r="Q21" s="22"/>
       <c r="R21" s="47"/>
       <c r="S21" s="47"/>
       <c r="T21" s="47"/>
     </row>
     <row r="22" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I22" s="56"/>
-      <c r="J22" s="57"/>
-      <c r="K22" s="57"/>
-      <c r="L22" s="57"/>
-      <c r="M22" s="57"/>
-      <c r="N22" s="57"/>
-      <c r="O22" s="58"/>
+      <c r="I22" s="55"/>
+      <c r="J22" s="56"/>
+      <c r="K22" s="56"/>
+      <c r="L22" s="56"/>
+      <c r="M22" s="56"/>
+      <c r="N22" s="56"/>
+      <c r="O22" s="57"/>
     </row>
     <row r="23" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I23" s="56"/>
-      <c r="J23" s="57"/>
-      <c r="K23" s="57"/>
-      <c r="L23" s="57"/>
-      <c r="M23" s="57"/>
-      <c r="N23" s="57"/>
-      <c r="O23" s="58"/>
+      <c r="I23" s="55"/>
+      <c r="J23" s="56"/>
+      <c r="K23" s="56"/>
+      <c r="L23" s="56"/>
+      <c r="M23" s="56"/>
+      <c r="N23" s="56"/>
+      <c r="O23" s="57"/>
     </row>
     <row r="24" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I24" s="59"/>
-      <c r="J24" s="60"/>
-      <c r="K24" s="60"/>
-      <c r="L24" s="60"/>
-      <c r="M24" s="60"/>
-      <c r="N24" s="60"/>
-      <c r="O24" s="61"/>
+      <c r="I24" s="58"/>
+      <c r="J24" s="59"/>
+      <c r="K24" s="59"/>
+      <c r="L24" s="59"/>
+      <c r="M24" s="59"/>
+      <c r="N24" s="59"/>
+      <c r="O24" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="R18:T18"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="Q13:T13"/>
     <mergeCell ref="D1:I1"/>
     <mergeCell ref="R21:T21"/>
     <mergeCell ref="B3:K3"/>
@@ -2606,14 +2608,6 @@
     <mergeCell ref="R20:T20"/>
     <mergeCell ref="R17:T17"/>
     <mergeCell ref="R19:T19"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="Q13:T13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="R18:T18"/>
-    <mergeCell ref="R16:T16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2637,13 +2631,13 @@
     <col min="8" max="8" width="11.109375" customWidth="1"/>
     <col min="9" max="9" width="9.33203125" customWidth="1"/>
     <col min="10" max="10" width="14.5546875" customWidth="1"/>
-    <col min="11" max="11" width="6.109375" customWidth="1"/>
-    <col min="12" max="12" width="6.44140625" customWidth="1"/>
-    <col min="13" max="13" width="5" customWidth="1"/>
+    <col min="11" max="12" width="22.6640625" customWidth="1"/>
+    <col min="13" max="14" width="27.21875" customWidth="1"/>
     <col min="15" max="15" width="11.88671875" customWidth="1"/>
     <col min="16" max="17" width="8.88671875" customWidth="1"/>
     <col min="21" max="21" width="9.109375" customWidth="1"/>
-    <col min="22" max="24" width="2.109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="2.109375" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="3.5546875" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="2.109375" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="4.109375" bestFit="1" customWidth="1"/>
@@ -2660,174 +2654,174 @@
       <c r="G1" s="46"/>
     </row>
     <row r="3" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="52"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="50"/>
     </row>
     <row r="5" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B5" s="7"/>
     </row>
     <row r="6" spans="2:30" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="68" t="s">
+      <c r="B6" s="75" t="s">
         <v>37</v>
       </c>
       <c r="C6" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" s="75" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="72" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="73"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="73"/>
+      <c r="K6" s="73"/>
+      <c r="L6" s="73"/>
+      <c r="M6" s="73"/>
+      <c r="N6" s="73"/>
+      <c r="O6" s="73"/>
+      <c r="P6" s="73"/>
+      <c r="Q6" s="73"/>
+      <c r="R6" s="73"/>
+      <c r="S6" s="73"/>
+      <c r="T6" s="73"/>
+      <c r="U6" s="73"/>
+      <c r="V6" s="73"/>
+      <c r="W6" s="73"/>
+      <c r="X6" s="73"/>
+      <c r="Y6" s="73"/>
+      <c r="Z6" s="73"/>
+      <c r="AA6" s="73"/>
+      <c r="AB6" s="73"/>
+      <c r="AC6" s="73"/>
+      <c r="AD6" s="74"/>
+    </row>
+    <row r="7" spans="2:30" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B7" s="75"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="75"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="67" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="69" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="70"/>
+      <c r="I7" s="70"/>
+      <c r="J7" s="70"/>
+      <c r="K7" s="70"/>
+      <c r="L7" s="70"/>
+      <c r="M7" s="70"/>
+      <c r="N7" s="70"/>
+      <c r="O7" s="70"/>
+      <c r="P7" s="70"/>
+      <c r="Q7" s="70"/>
+      <c r="R7" s="71"/>
+      <c r="S7" s="64" t="s">
+        <v>43</v>
+      </c>
+      <c r="T7" s="64"/>
+      <c r="U7" s="64"/>
+      <c r="V7" s="64"/>
+      <c r="W7" s="64"/>
+      <c r="X7" s="63" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y7" s="63"/>
+      <c r="Z7" s="63"/>
+      <c r="AA7" s="63"/>
+      <c r="AB7" s="63"/>
+      <c r="AC7" s="63"/>
+      <c r="AD7" s="63"/>
+    </row>
+    <row r="8" spans="2:30" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="75"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="65" t="s">
         <v>93</v>
       </c>
-      <c r="D6" s="68" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" s="69" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="63" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
-      <c r="L6" s="64"/>
-      <c r="M6" s="64"/>
-      <c r="N6" s="64"/>
-      <c r="O6" s="64"/>
-      <c r="P6" s="64"/>
-      <c r="Q6" s="64"/>
-      <c r="R6" s="64"/>
-      <c r="S6" s="64"/>
-      <c r="T6" s="64"/>
-      <c r="U6" s="64"/>
-      <c r="V6" s="64"/>
-      <c r="W6" s="64"/>
-      <c r="X6" s="64"/>
-      <c r="Y6" s="64"/>
-      <c r="Z6" s="64"/>
-      <c r="AA6" s="64"/>
-      <c r="AB6" s="64"/>
-      <c r="AC6" s="64"/>
-      <c r="AD6" s="65"/>
-    </row>
-    <row r="7" spans="2:30" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="68"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="68"/>
-      <c r="E7" s="70"/>
-      <c r="F7" s="76" t="s">
-        <v>41</v>
-      </c>
-      <c r="G7" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="H7" s="77"/>
-      <c r="I7" s="77"/>
-      <c r="J7" s="77"/>
-      <c r="K7" s="77"/>
-      <c r="L7" s="77"/>
-      <c r="M7" s="77"/>
-      <c r="N7" s="77"/>
-      <c r="O7" s="77"/>
-      <c r="P7" s="77"/>
-      <c r="Q7" s="77"/>
-      <c r="R7" s="67"/>
-      <c r="S7" s="75" t="s">
-        <v>43</v>
-      </c>
-      <c r="T7" s="75"/>
-      <c r="U7" s="75"/>
-      <c r="V7" s="75"/>
-      <c r="W7" s="75"/>
-      <c r="X7" s="71" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y7" s="71"/>
-      <c r="Z7" s="71"/>
-      <c r="AA7" s="71"/>
-      <c r="AB7" s="71"/>
-      <c r="AC7" s="71"/>
-      <c r="AD7" s="71"/>
-    </row>
-    <row r="8" spans="2:30" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="68"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="72" t="s">
+      <c r="E8" s="65" t="s">
         <v>94</v>
       </c>
-      <c r="E8" s="72" t="s">
+      <c r="F8" s="67"/>
+      <c r="G8" s="68" t="s">
         <v>95</v>
       </c>
-      <c r="F8" s="76"/>
-      <c r="G8" s="74" t="s">
+      <c r="H8" s="68"/>
+      <c r="I8" s="68" t="s">
         <v>96</v>
       </c>
-      <c r="H8" s="74"/>
-      <c r="I8" s="74" t="s">
+      <c r="J8" s="68"/>
+      <c r="K8" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="J8" s="74"/>
-      <c r="K8" s="74" t="s">
+      <c r="L8" s="68"/>
+      <c r="M8" s="69" t="s">
         <v>98</v>
       </c>
-      <c r="L8" s="74"/>
-      <c r="M8" s="66" t="s">
+      <c r="N8" s="71"/>
+      <c r="O8" s="69" t="s">
+        <v>124</v>
+      </c>
+      <c r="P8" s="71"/>
+      <c r="Q8" s="68" t="s">
         <v>99</v>
       </c>
-      <c r="N8" s="67"/>
-      <c r="O8" s="66" t="s">
-        <v>100</v>
-      </c>
-      <c r="P8" s="67"/>
-      <c r="Q8" s="74" t="s">
-        <v>101</v>
-      </c>
-      <c r="R8" s="74"/>
-      <c r="S8" s="75" t="s">
+      <c r="R8" s="68"/>
+      <c r="S8" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="T8" s="75" t="s">
+      <c r="T8" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="U8" s="75" t="s">
+      <c r="U8" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="V8" s="75" t="s">
-        <v>89</v>
-      </c>
-      <c r="W8" s="75" t="s">
-        <v>91</v>
-      </c>
-      <c r="X8" s="71">
+      <c r="V8" s="64" t="s">
+        <v>88</v>
+      </c>
+      <c r="W8" s="64" t="s">
+        <v>90</v>
+      </c>
+      <c r="X8" s="63">
         <v>0</v>
       </c>
-      <c r="Y8" s="71">
+      <c r="Y8" s="63">
         <v>1</v>
       </c>
-      <c r="Z8" s="71">
+      <c r="Z8" s="63">
         <v>2</v>
       </c>
-      <c r="AA8" s="71" t="s">
+      <c r="AA8" s="63" t="s">
         <v>45</v>
       </c>
-      <c r="AB8" s="71" t="s">
+      <c r="AB8" s="63" t="s">
         <v>46</v>
       </c>
-      <c r="AC8" s="71" t="s">
+      <c r="AC8" s="63" t="s">
         <v>47</v>
       </c>
-      <c r="AD8" s="71" t="s">
+      <c r="AD8" s="63" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9" spans="2:30" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="68"/>
+      <c r="B9" s="75"/>
       <c r="C9" s="28"/>
-      <c r="D9" s="73"/>
-      <c r="E9" s="73"/>
-      <c r="F9" s="76"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="67"/>
       <c r="G9" s="29" t="s">
         <v>49</v>
       </c>
@@ -2864,37 +2858,37 @@
       <c r="R9" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="S9" s="75"/>
-      <c r="T9" s="75"/>
-      <c r="U9" s="75"/>
-      <c r="V9" s="75"/>
-      <c r="W9" s="75"/>
-      <c r="X9" s="71"/>
-      <c r="Y9" s="71"/>
-      <c r="Z9" s="71"/>
-      <c r="AA9" s="71"/>
-      <c r="AB9" s="71"/>
-      <c r="AC9" s="71"/>
-      <c r="AD9" s="71"/>
+      <c r="S9" s="64"/>
+      <c r="T9" s="64"/>
+      <c r="U9" s="64"/>
+      <c r="V9" s="64"/>
+      <c r="W9" s="64"/>
+      <c r="X9" s="63"/>
+      <c r="Y9" s="63"/>
+      <c r="Z9" s="63"/>
+      <c r="AA9" s="63"/>
+      <c r="AB9" s="63"/>
+      <c r="AC9" s="63"/>
+      <c r="AD9" s="63"/>
     </row>
     <row r="10" spans="2:30" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B10" s="31" t="s">
         <v>51</v>
       </c>
       <c r="C10" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="D10" s="31" t="s">
+      <c r="F10" s="33" t="s">
         <v>103</v>
       </c>
-      <c r="E10" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="F10" s="33" t="s">
-        <v>105</v>
-      </c>
       <c r="G10" s="34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H10" s="34"/>
       <c r="I10" s="34"/>
@@ -2908,14 +2902,14 @@
       <c r="Q10" s="34"/>
       <c r="R10" s="34"/>
       <c r="S10" s="35" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T10" s="35"/>
       <c r="U10" s="35"/>
       <c r="V10" s="35"/>
       <c r="W10" s="35"/>
       <c r="X10" s="36" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="Y10" s="36"/>
       <c r="Z10" s="36"/>
@@ -2923,58 +2917,58 @@
       <c r="AB10" s="36"/>
       <c r="AC10" s="36"/>
       <c r="AD10" s="36" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="2:30" ht="46.8" x14ac:dyDescent="0.3">
       <c r="B11" s="31" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D11" s="31" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="F11" s="33" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G11" s="34"/>
       <c r="H11" s="34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I11" s="34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J11" s="34"/>
       <c r="K11" s="34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L11" s="34"/>
       <c r="M11" s="34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="N11" s="34"/>
       <c r="O11" s="34"/>
       <c r="P11" s="34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="Q11" s="34"/>
       <c r="R11" s="34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="S11" s="35"/>
       <c r="T11" s="35"/>
       <c r="U11" s="35"/>
       <c r="V11" s="35"/>
       <c r="W11" s="35" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="X11" s="36" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="Y11" s="36"/>
       <c r="Z11" s="36"/>
@@ -2982,91 +2976,91 @@
       <c r="AB11" s="36"/>
       <c r="AC11" s="36"/>
       <c r="AD11" s="36" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="2:30" ht="62.4" x14ac:dyDescent="0.3">
       <c r="B12" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="E12" s="38" t="s">
+        <v>102</v>
+      </c>
+      <c r="F12" s="33" t="s">
         <v>108</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>109</v>
-      </c>
-      <c r="D12" s="37" t="s">
-        <v>110</v>
-      </c>
-      <c r="E12" s="38" t="s">
-        <v>104</v>
-      </c>
-      <c r="F12" s="33" t="s">
-        <v>111</v>
       </c>
       <c r="G12" s="34"/>
       <c r="H12" s="34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I12" s="34"/>
       <c r="J12" s="34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K12" s="34"/>
       <c r="L12" s="34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="M12" s="34"/>
       <c r="N12" s="34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="O12" s="34"/>
       <c r="P12" s="34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="Q12" s="34"/>
       <c r="R12" s="34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="S12" s="35"/>
       <c r="T12" s="35" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U12" s="35"/>
       <c r="V12" s="35"/>
       <c r="W12" s="35"/>
       <c r="X12" s="36"/>
       <c r="Y12" s="36" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="Z12" s="36"/>
       <c r="AA12" s="36"/>
       <c r="AB12" s="36" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="AC12" s="36"/>
       <c r="AD12" s="36"/>
     </row>
     <row r="13" spans="2:30" ht="46.8" x14ac:dyDescent="0.3">
       <c r="B13" s="31" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D13" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="E13" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="F13" s="33" t="s">
         <v>110</v>
-      </c>
-      <c r="E13" s="32" t="s">
-        <v>113</v>
-      </c>
-      <c r="F13" s="33" t="s">
-        <v>114</v>
       </c>
       <c r="G13" s="34"/>
       <c r="H13" s="34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I13" s="34"/>
       <c r="J13" s="34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K13" s="34"/>
       <c r="L13" s="34"/>
@@ -3075,18 +3069,18 @@
       <c r="O13" s="34"/>
       <c r="P13" s="34"/>
       <c r="Q13" s="34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="R13" s="34"/>
       <c r="S13" s="35"/>
       <c r="T13" s="35"/>
       <c r="U13" s="35"/>
       <c r="V13" s="35" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="W13" s="35"/>
       <c r="X13" s="36" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="Y13" s="36"/>
       <c r="Z13" s="36"/>
@@ -3097,41 +3091,41 @@
     </row>
     <row r="14" spans="2:30" ht="46.8" x14ac:dyDescent="0.3">
       <c r="B14" s="31" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G14" s="34"/>
       <c r="H14" s="34"/>
       <c r="I14" s="34"/>
       <c r="J14" s="34"/>
       <c r="K14" s="34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L14" s="34"/>
       <c r="M14" s="34"/>
       <c r="N14" s="34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="O14" s="34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="P14" s="34"/>
       <c r="Q14" s="34"/>
       <c r="R14" s="34"/>
       <c r="S14" s="35"/>
       <c r="T14" s="35" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U14" s="35"/>
       <c r="V14" s="35"/>
@@ -3139,62 +3133,62 @@
       <c r="X14" s="36"/>
       <c r="Y14" s="36"/>
       <c r="Z14" s="36" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="AA14" s="36"/>
       <c r="AB14" s="36" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="AC14" s="36"/>
       <c r="AD14" s="36"/>
     </row>
     <row r="15" spans="2:30" ht="46.8" x14ac:dyDescent="0.3">
       <c r="B15" s="31" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="F15" s="33" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G15" s="34"/>
       <c r="H15" s="34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I15" s="34"/>
       <c r="J15" s="34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K15" s="34"/>
       <c r="L15" s="34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="M15" s="34"/>
       <c r="N15" s="34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="O15" s="34"/>
       <c r="P15" s="34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="Q15" s="34"/>
       <c r="R15" s="34"/>
       <c r="S15" s="35"/>
       <c r="T15" s="35"/>
       <c r="U15" s="35" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="V15" s="35"/>
       <c r="W15" s="35"/>
       <c r="X15" s="36" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="Y15" s="36"/>
       <c r="Z15" s="36"/>
@@ -3208,6 +3202,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="X7:AD7"/>
+    <mergeCell ref="AD8:AD9"/>
     <mergeCell ref="D1:G1"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="X8:X9"/>
@@ -3224,20 +3232,6 @@
     <mergeCell ref="G7:R7"/>
     <mergeCell ref="F6:AD6"/>
     <mergeCell ref="M8:N8"/>
-    <mergeCell ref="O8:P8"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="X7:AD7"/>
-    <mergeCell ref="AD8:AD9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3275,161 +3269,161 @@
       <c r="G1" s="46"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="78" t="s">
+      <c r="B3" s="102" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="102"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="102"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="102"/>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B4" s="103" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="78"/>
-      <c r="K3" s="78"/>
-      <c r="L3" s="78"/>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B4" s="79" t="s">
+      <c r="C4" s="83" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="86" t="s">
+      <c r="D4" s="111" t="s">
         <v>55</v>
       </c>
-      <c r="D4" s="88" t="s">
+      <c r="E4" s="105" t="s">
         <v>56</v>
       </c>
-      <c r="E4" s="81" t="s">
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="106"/>
+      <c r="K4" s="105" t="s">
         <v>57</v>
       </c>
-      <c r="F4" s="85"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="85"/>
-      <c r="I4" s="85"/>
-      <c r="J4" s="82"/>
-      <c r="K4" s="81" t="s">
+      <c r="L4" s="106"/>
+    </row>
+    <row r="5" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="104"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="112"/>
+      <c r="E5" s="113" t="s">
+        <v>93</v>
+      </c>
+      <c r="F5" s="114"/>
+      <c r="G5" s="114"/>
+      <c r="H5" s="114"/>
+      <c r="I5" s="114"/>
+      <c r="J5" s="115"/>
+      <c r="K5" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="L4" s="82"/>
-    </row>
-    <row r="5" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="80"/>
-      <c r="C5" s="87"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="90" t="s">
-        <v>94</v>
-      </c>
-      <c r="F5" s="91"/>
-      <c r="G5" s="91"/>
-      <c r="H5" s="91"/>
-      <c r="I5" s="91"/>
-      <c r="J5" s="92"/>
-      <c r="K5" s="39" t="s">
+      <c r="L5" s="39" t="s">
         <v>59</v>
-      </c>
-      <c r="L5" s="39" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="6" spans="2:14" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B6" s="41">
         <v>9</v>
       </c>
-      <c r="C6" s="83" t="s">
-        <v>61</v>
+      <c r="C6" s="107" t="s">
+        <v>60</v>
       </c>
       <c r="D6" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="E6" s="93" t="s">
-        <v>123</v>
-      </c>
-      <c r="F6" s="94"/>
-      <c r="G6" s="94"/>
-      <c r="H6" s="94"/>
-      <c r="I6" s="94"/>
-      <c r="J6" s="95"/>
+      <c r="E6" s="116" t="s">
+        <v>117</v>
+      </c>
+      <c r="F6" s="117"/>
+      <c r="G6" s="117"/>
+      <c r="H6" s="117"/>
+      <c r="I6" s="117"/>
+      <c r="J6" s="118"/>
       <c r="K6" s="32" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="L6" s="41" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="2:14" ht="78" x14ac:dyDescent="0.3">
       <c r="B7" s="41">
         <v>10</v>
       </c>
-      <c r="C7" s="83"/>
+      <c r="C7" s="107"/>
       <c r="D7" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="E7" s="81" t="s">
-        <v>129</v>
-      </c>
-      <c r="F7" s="85"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="85"/>
-      <c r="I7" s="85"/>
-      <c r="J7" s="82"/>
+        <v>61</v>
+      </c>
+      <c r="E7" s="105" t="s">
+        <v>123</v>
+      </c>
+      <c r="F7" s="109"/>
+      <c r="G7" s="109"/>
+      <c r="H7" s="109"/>
+      <c r="I7" s="109"/>
+      <c r="J7" s="106"/>
       <c r="K7" s="32" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="L7" s="32" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B8" s="41">
         <v>11</v>
       </c>
-      <c r="C8" s="83"/>
+      <c r="C8" s="107"/>
       <c r="D8" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="E8" s="81" t="s">
-        <v>125</v>
-      </c>
-      <c r="F8" s="85"/>
-      <c r="G8" s="85"/>
-      <c r="H8" s="85"/>
-      <c r="I8" s="85"/>
-      <c r="J8" s="82"/>
+        <v>118</v>
+      </c>
+      <c r="E8" s="105" t="s">
+        <v>119</v>
+      </c>
+      <c r="F8" s="109"/>
+      <c r="G8" s="109"/>
+      <c r="H8" s="109"/>
+      <c r="I8" s="109"/>
+      <c r="J8" s="106"/>
       <c r="K8" s="32" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="L8" s="41" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="2:14" ht="62.4" x14ac:dyDescent="0.3">
       <c r="B9" s="41">
         <v>12</v>
       </c>
-      <c r="C9" s="83"/>
+      <c r="C9" s="107"/>
       <c r="D9" s="40" t="s">
-        <v>126</v>
-      </c>
-      <c r="E9" s="81" t="s">
-        <v>125</v>
-      </c>
-      <c r="F9" s="85"/>
-      <c r="G9" s="85"/>
-      <c r="H9" s="85"/>
-      <c r="I9" s="85"/>
-      <c r="J9" s="82"/>
+        <v>120</v>
+      </c>
+      <c r="E9" s="105" t="s">
+        <v>127</v>
+      </c>
+      <c r="F9" s="109"/>
+      <c r="G9" s="109"/>
+      <c r="H9" s="109"/>
+      <c r="I9" s="109"/>
+      <c r="J9" s="106"/>
       <c r="K9" s="32" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="L9" s="41" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="39">
         <v>13</v>
       </c>
-      <c r="C10" s="84"/>
+      <c r="C10" s="108"/>
       <c r="D10" s="30" t="s">
         <v>22</v>
       </c>
@@ -3471,88 +3465,88 @@
     </row>
     <row r="12" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="K12" s="10"/>
+    </row>
+    <row r="13" spans="2:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="78" t="s">
         <v>63</v>
       </c>
-      <c r="K12" s="10"/>
-    </row>
-    <row r="13" spans="2:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="111" t="s">
+      <c r="C13" s="79"/>
+      <c r="D13" s="79"/>
+      <c r="E13" s="79"/>
+      <c r="F13" s="80" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="112"/>
-      <c r="D13" s="112"/>
-      <c r="E13" s="112"/>
-      <c r="F13" s="104" t="s">
+      <c r="G13" s="81"/>
+      <c r="H13" s="78" t="s">
         <v>65</v>
       </c>
-      <c r="G13" s="105"/>
-      <c r="H13" s="111" t="s">
+      <c r="I13" s="79"/>
+      <c r="J13" s="79"/>
+      <c r="K13" s="79"/>
+      <c r="L13" s="91"/>
+      <c r="M13" s="96" t="s">
         <v>66</v>
       </c>
-      <c r="I13" s="112"/>
-      <c r="J13" s="112"/>
-      <c r="K13" s="112"/>
-      <c r="L13" s="113"/>
-      <c r="M13" s="117" t="s">
+      <c r="N13" s="97"/>
+    </row>
+    <row r="14" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="95" t="s">
         <v>67</v>
       </c>
-      <c r="N13" s="118"/>
-    </row>
-    <row r="14" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="96" t="s">
+      <c r="C14" s="87" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="98" t="s">
+      <c r="D14" s="87" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="98" t="s">
+      <c r="E14" s="99" t="s">
         <v>70</v>
       </c>
-      <c r="E14" s="100" t="s">
+      <c r="F14" s="84" t="s">
         <v>71</v>
       </c>
-      <c r="F14" s="102" t="s">
+      <c r="G14" s="82" t="s">
         <v>72</v>
       </c>
-      <c r="G14" s="106" t="s">
+      <c r="H14" s="85" t="s">
         <v>73</v>
       </c>
-      <c r="H14" s="107" t="s">
+      <c r="I14" s="87" t="s">
+        <v>67</v>
+      </c>
+      <c r="J14" s="87" t="s">
+        <v>68</v>
+      </c>
+      <c r="K14" s="89" t="s">
         <v>74</v>
       </c>
-      <c r="I14" s="98" t="s">
-        <v>68</v>
-      </c>
-      <c r="J14" s="98" t="s">
-        <v>69</v>
-      </c>
-      <c r="K14" s="109" t="s">
+      <c r="L14" s="92" t="s">
         <v>75</v>
       </c>
-      <c r="L14" s="114" t="s">
+      <c r="M14" s="94" t="s">
         <v>76</v>
       </c>
-      <c r="M14" s="116" t="s">
+      <c r="N14" s="83" t="s">
         <v>77</v>
       </c>
-      <c r="N14" s="86" t="s">
-        <v>78</v>
-      </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B15" s="97"/>
-      <c r="C15" s="99"/>
-      <c r="D15" s="99"/>
-      <c r="E15" s="101"/>
-      <c r="F15" s="103"/>
-      <c r="G15" s="106"/>
-      <c r="H15" s="108"/>
-      <c r="I15" s="99"/>
-      <c r="J15" s="99"/>
-      <c r="K15" s="110"/>
-      <c r="L15" s="115"/>
-      <c r="M15" s="96"/>
-      <c r="N15" s="102"/>
+      <c r="B15" s="98"/>
+      <c r="C15" s="88"/>
+      <c r="D15" s="88"/>
+      <c r="E15" s="100"/>
+      <c r="F15" s="101"/>
+      <c r="G15" s="82"/>
+      <c r="H15" s="86"/>
+      <c r="I15" s="88"/>
+      <c r="J15" s="88"/>
+      <c r="K15" s="90"/>
+      <c r="L15" s="93"/>
+      <c r="M15" s="95"/>
+      <c r="N15" s="84"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B16" s="14">
@@ -3571,10 +3565,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I16" s="14">
         <v>0</v>
@@ -3589,7 +3583,7 @@
         <v>100</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N16" s="17">
         <v>4</v>
@@ -3597,6 +3591,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="C6:C10"/>
+    <mergeCell ref="E4:J4"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E5:J5"/>
+    <mergeCell ref="E6:J6"/>
+    <mergeCell ref="E7:J7"/>
+    <mergeCell ref="E8:J8"/>
+    <mergeCell ref="E9:J9"/>
     <mergeCell ref="D1:G1"/>
     <mergeCell ref="B13:E13"/>
     <mergeCell ref="F13:G13"/>
@@ -3613,20 +3621,6 @@
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="C14:C15"/>
     <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="C6:C10"/>
-    <mergeCell ref="E4:J4"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E5:J5"/>
-    <mergeCell ref="E6:J6"/>
-    <mergeCell ref="E7:J7"/>
-    <mergeCell ref="E8:J8"/>
-    <mergeCell ref="E9:J9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3634,15 +3628,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010058284A30843C9F43BD758DDD8294D484" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2e00392fbb7f49de63e89755c965b762">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fed1744a-f275-4023-9290-77fd546fd730" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="37d4e1d93698397f16b7bbb6f83014a7" ns2:_="">
     <xsd:import namespace="fed1744a-f275-4023-9290-77fd546fd730"/>
@@ -3810,6 +3795,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -3817,14 +3811,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5426D20B-58AE-4BE9-8733-DFB2BC19D8C6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{845501DA-8B32-4FE5-8083-FBCE9B17F25B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3842,6 +3828,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5426D20B-58AE-4BE9-8733-DFB2BC19D8C6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6597AB9C-DC10-4824-8900-518D3B18165A}">
   <ds:schemaRefs>
